--- a/.claude/skills/fill-table-definition/tmp_テーブル定義書.xlsx
+++ b/.claude/skills/fill-table-definition/tmp_テーブル定義書.xlsx
@@ -802,13 +802,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="5" customWidth="1" style="14" min="1" max="1"/>
     <col width="48" customWidth="1" style="14" min="2" max="2"/>
     <col width="24" customWidth="1" style="14" min="3" max="3"/>
     <col width="56" customWidth="1" style="14" min="4" max="4"/>
+    <col width="16" customWidth="1" style="14" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="52.60000000000001" customHeight="1" s="14">
@@ -837,6 +838,11 @@
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>用途・概要</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>リンク</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1029,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="33.7" customHeight="1" s="14">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -1084,7 +1089,6 @@
       <c r="J5" s="21" t="n"/>
       <c r="K5" s="22" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="32" customHeight="1" s="14">
       <c r="A7" s="5" t="inlineStr">
         <is>
